--- a/Pruned AI Models_Table.xlsx
+++ b/Pruned AI Models_Table.xlsx
@@ -742,7 +742,7 @@
       <c r="P3" s="30" t="n"/>
       <c r="Q3" s="32" t="inlineStr">
         <is>
-          <t>https://developers.openai.com/api/docs/models/gpt-6-astra</t>
+          <t>https://deploymentsafety.openai.com/gpt-6-astra/gpt-6-astra.pdf</t>
         </is>
       </c>
       <c r="R3" s="31" t="inlineStr">
@@ -783,7 +783,9 @@
           <t>MoE</t>
         </is>
       </c>
-      <c r="G4" s="28" t="n"/>
+      <c r="G4" s="28" t="n">
+        <v>250000</v>
+      </c>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="29" t="n">
         <v>166.7</v>

--- a/Pruned AI Models_Table.xlsx
+++ b/Pruned AI Models_Table.xlsx
@@ -24686,7 +24686,7 @@
       </c>
       <c r="O343" s="30" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟢</t>
         </is>
       </c>
       <c r="P343" s="30" t="inlineStr">
@@ -24706,7 +24706,7 @@
       </c>
       <c r="S343" s="33" t="inlineStr">
         <is>
-          <t>gpt-4o-2024-05-13 no longer easily available, so hidden in the Model Table rankings. Omnimodel. ‘[GPT-4o is] likely an early checkpoint of GPT-5’. https://twitter.com/drjimfan/status/1790089671365767313 ELO: https://twitter.com/LiamFedus/status/1790064963966370209 Demo: https://youtu.be/DQacCB9tDaw</t>
+          <t>gpt-4o-2024-05-13 no longer easily available, so hidden in the Model Table rankings. Omnimodel. ‘[GPT-4o is] likely an early checkpoint of GPT-5’. https://twitter.com/drjimfan/status/1790089671365767313 ELO: https://twitter.com/LiamFedus/status/1790064963966370209 Demo: https://youtu.be/DQacCB9tDaw Public? changed from 🔴 to 🟢 on 2026-09-27: OpenAI's launch post says GPT-4o's text and image capabilities started rolling out in ChatGPT, including the free tier, and in the API on 2024-05-13. Source: https://openai.com/index/hello-gpt-4o/.</t>
         </is>
       </c>
       <c r="T343" s="31" t="n">
